--- a/docs/tcm_accuracy.xlsx
+++ b/docs/tcm_accuracy.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gesom\github\TCM_AI\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF57F9E7-09D2-449B-B7F1-353C9F6C7398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TCM Accuracy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TCM Accuracy" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>Modell</t>
   </si>
@@ -86,22 +89,36 @@
   </si>
   <si>
     <t>TCM-o5-pro</t>
+  </si>
+  <si>
+    <t>TCM-o5.1-mini</t>
+  </si>
+  <si>
+    <t>TCM-o5.1</t>
+  </si>
+  <si>
+    <t>TCM-o5.1-pro</t>
+  </si>
+  <si>
+    <t>o5.1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color indexed="65"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -120,31 +137,28 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0">
-      <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -152,16 +166,20 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="c14">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
@@ -173,12 +191,13 @@
       <c:tx>
         <c:rich>
           <a:bodyPr/>
+          <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr sz="2000" b="0" i="0">
+              <a:rPr lang="de-CH" sz="2000" b="0" i="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -188,16 +207,16 @@
               </a:rPr>
               <a:t>Testing Accuracy of TCM Models</a:t>
             </a:r>
-            <a:endParaRPr sz="2600" b="0" i="0">
+            <a:endParaRPr lang="de-CH" sz="2600" b="0" i="0">
               <a:latin typeface="Open Sans Extrabold"/>
               <a:cs typeface="Open Sans Extrabold"/>
             </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
@@ -210,16 +229,25 @@
           <c:tx>
             <c:strRef>
               <c:f>'TCM Accuracy'!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Genauigkeit</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr bwMode="auto">
+          <c:spPr>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:dPt>
             <c:idx val="0"/>
-            <c:spPr bwMode="auto">
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -230,10 +258,17 @@
                 <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
-            <c:spPr bwMode="auto">
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -244,10 +279,17 @@
                 <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
-            <c:spPr bwMode="auto">
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -258,10 +300,17 @@
                 <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
-            <c:spPr bwMode="auto">
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -272,10 +321,17 @@
                 <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
-            <c:spPr bwMode="auto">
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -286,10 +342,17 @@
                 <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
-            <c:spPr bwMode="auto">
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -300,10 +363,17 @@
                 <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
-            <c:spPr bwMode="auto">
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -314,10 +384,17 @@
                 <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
-            <c:spPr bwMode="auto">
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -328,10 +405,17 @@
                 <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
-            <c:spPr bwMode="auto">
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -342,10 +426,17 @@
                 <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
-            <c:spPr bwMode="auto">
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -356,10 +447,17 @@
                 <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
-            <c:spPr bwMode="auto">
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -370,10 +468,17 @@
                 <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
-            <c:spPr bwMode="auto">
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -384,27 +489,231 @@
                 <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
-          </c:dPt>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="15"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="16"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001A-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="17"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-7C8C-43AA-92AC-46EF9E573588}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'TCM Accuracy'!$B$3:$B$17</c:f>
+              <c:f>'TCM Accuracy'!$B$3:$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>TCM-o1-mini</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>TCM-o1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>TCM-o1-pro</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>TCM-o2-mini</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>TCM-o2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>TCM-o2-pro</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>TCM-o3-mini</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>TCM-o3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>TCM-o3-pro</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>TCM-o4-mini</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>TCM-o4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>TCM-o4.1-pro</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>TCM-o5-mini</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>TCM-o5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>TCM-o5-pro</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>TCM-o5.1-mini</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>TCM-o5.1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>TCM-o5.1-pro</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TCM Accuracy'!$C$3:$C$17</c:f>
+              <c:f>'TCM Accuracy'!$C$3:$C$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>0.91849999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.91249999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.91449999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.92500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.93700000000000006</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.94850000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.94310000000000005</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.9526</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.96030000000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96079999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.96519999999999995</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.98319999999999996</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.98809999999999998</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.99019999999999997</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.99010000000000009</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.99360000000000004</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.99379999999999991</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.99370000000000003</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000018-7C8C-43AA-92AC-46EF9E573588}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:numFmt formatCode="0.00%"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showCatName val="0"/>
-          <c:showLeaderLines val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showPercent val="0"/>
-          <c:showSerName val="0"/>
-          <c:showVal val="1"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:axId val="10"/>
@@ -417,10 +726,14 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
         <c:crossAx val="100"/>
         <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
@@ -431,11 +744,11 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr bwMode="auto"/>
-        </c:majorGridlines>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
         <c:crossAx val="10"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
@@ -445,14 +758,16 @@
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
-  <c:spPr bwMode="auto">
-    <a:xfrm rot="0"/>
-  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -461,14 +776,23 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6480000" cy="4320000"/>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm/>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -480,291 +804,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -980,24 +1021,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:D20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="3"/>
-    <col customWidth="1" min="2" max="2" width="18"/>
-    <col customWidth="1" min="3" max="3" width="12"/>
-    <col customWidth="1" min="4" max="4" width="10"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1008,7 +1047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -1019,7 +1058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -1030,7 +1069,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -1041,7 +1080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>7</v>
       </c>
@@ -1052,7 +1091,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>9</v>
       </c>
@@ -1063,7 +1102,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>10</v>
       </c>
@@ -1074,7 +1113,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>11</v>
       </c>
@@ -1085,7 +1124,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>13</v>
       </c>
@@ -1096,7 +1135,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>14</v>
       </c>
@@ -1107,7 +1146,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>15</v>
       </c>
@@ -1118,7 +1157,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>17</v>
       </c>
@@ -1129,7 +1168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>18</v>
       </c>
@@ -1140,7 +1179,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" ht="14.25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>19</v>
       </c>
@@ -1151,8 +1190,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" ht="14.25">
-      <c r="B16" s="4" t="s">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="3">
@@ -1162,8 +1201,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" ht="14.25">
-      <c r="B17" s="4" t="s">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
         <v>22</v>
       </c>
       <c r="C17" s="3">
@@ -1173,11 +1212,42 @@
         <v>20</v>
       </c>
     </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.99360000000000004</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.99379999999999991</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.99370000000000003</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/tcm_accuracy.xlsx
+++ b/docs/tcm_accuracy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gesom\github\TCM_AI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF57F9E7-09D2-449B-B7F1-353C9F6C7398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB86082-3403-4F7D-B079-58E1762C1E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="29">
   <si>
     <t>Modell</t>
   </si>
@@ -101,6 +101,12 @@
   </si>
   <si>
     <t>o5.1</t>
+  </si>
+  <si>
+    <t>TCM-05.2-mini</t>
+  </si>
+  <si>
+    <t>o5.2</t>
   </si>
 </sst>
 </file>
@@ -578,9 +584,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'TCM Accuracy'!$B$3:$B$20</c:f>
+              <c:f>'TCM Accuracy'!$B$3:$B$21</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>TCM-o1-mini</c:v>
                 </c:pt>
@@ -634,16 +640,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>TCM-o5.1-pro</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>TCM-05.2-mini</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TCM Accuracy'!$C$3:$C$20</c:f>
+              <c:f>'TCM Accuracy'!$C$3:$C$21</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.91849999999999998</c:v>
                 </c:pt>
@@ -697,6 +706,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0.99370000000000003</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.99470000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1027,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:D20"/>
+  <dimension ref="B2:D21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -1245,6 +1257,17 @@
         <v>26</v>
       </c>
     </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.99470000000000003</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/docs/tcm_accuracy.xlsx
+++ b/docs/tcm_accuracy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gesom\github\TCM_AI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB86082-3403-4F7D-B079-58E1762C1E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45580FF7-6E90-4434-8AFD-B54AE5B1D28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,10 +103,10 @@
     <t>o5.1</t>
   </si>
   <si>
-    <t>TCM-05.2-mini</t>
-  </si>
-  <si>
     <t>o5.2</t>
+  </si>
+  <si>
+    <t>TCM-05.2</t>
   </si>
 </sst>
 </file>
@@ -642,7 +642,7 @@
                   <c:v>TCM-o5.1-pro</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>TCM-05.2-mini</c:v>
+                  <c:v>TCM-05.2</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -708,7 +708,7 @@
                   <c:v>0.99370000000000003</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.99470000000000003</c:v>
+                  <c:v>0.99590000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1259,13 +1259,13 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.99590000000000001</v>
+      </c>
+      <c r="D21" t="s">
         <v>27</v>
-      </c>
-      <c r="C21" s="3">
-        <v>0.99470000000000003</v>
-      </c>
-      <c r="D21" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
